--- a/excel_routes/route_AHB_HMB_threats.xlsx
+++ b/excel_routes/route_AHB_HMB_threats.xlsx
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1271</v>
+        <v>1101</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1502</v>
+        <v>1312</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-231</v>
+        <v>-211</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>

--- a/excel_routes/route_AHB_HMB_threats.xlsx
+++ b/excel_routes/route_AHB_HMB_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +86,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -537,13 +546,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1101</v>
+        <v>971</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1312</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-211</v>
+        <v>-341</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -560,6 +569,96 @@
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>19-JUL-26</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>SM-446</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-144</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>671</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>1221</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>-550</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>19-JUL-26</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>SM-446</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-346</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>738</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>1221</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>-483</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_AHB_HMB_threats.xlsx
+++ b/excel_routes/route_AHB_HMB_threats.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -636,22 +636,22 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>738</v>
+        <v>915</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1221</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-483</v>
+        <v>-306</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -659,6 +659,51 @@
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>19-JUL-26</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SM-446</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-342</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>985</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>1221</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>-236</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_AHB_HMB_threats.xlsx
+++ b/excel_routes/route_AHB_HMB_threats.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -619,96 +619,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>19-JUL-26</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>SM-446</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-346</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>915</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>1221</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>-306</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>19-JUL-26</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>SM-446</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-342</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>985</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>1221</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>-236</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/excel_routes/route_AHB_HMB_threats.xlsx
+++ b/excel_routes/route_AHB_HMB_threats.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -546,13 +546,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>971</v>
+        <v>1101</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1312</v>
+        <v>1368</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-341</v>
+        <v>-267</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -591,13 +591,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>671</v>
+        <v>763</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1221</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-550</v>
+        <v>-458</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -614,6 +614,96 @@
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>19-JUL-26</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>SM-446</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-346</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>915</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>1221</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>-306</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>19-JUL-26</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SM-446</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-342</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>985</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>1221</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>-236</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_AHB_HMB_threats.xlsx
+++ b/excel_routes/route_AHB_HMB_threats.xlsx
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -546,13 +546,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1101</v>
+        <v>406</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1368</v>
+        <v>653</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-267</v>
+        <v>-247</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -577,7 +577,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>19-JUL-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -591,13 +591,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>763</v>
+        <v>971</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1221</v>
+        <v>1368</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-458</v>
+        <v>-397</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -608,9 +608,9 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -636,22 +636,22 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>915</v>
+        <v>738</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1221</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-306</v>
+        <v>-483</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -677,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-342</t>
+          <t>Nile Air NP-144</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>985</v>
+        <v>763</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1221</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-236</v>
+        <v>-458</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -698,9 +698,9 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
